--- a/www/download/IND.labour_force_value.s.mv.EXI382.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11312.783</t>
+          <t>12633720243.8769</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8816.216</t>
+          <t>9613356583.54228</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12036.821</t>
+          <t>12627556598.6393</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9944.37</t>
+          <t>10712157892.922</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14654.586</t>
+          <t>15895166526.8692</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11730.048</t>
+          <t>12919261120.4873</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11677.21</t>
+          <t>12891277695.2379</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11727.647</t>
+          <t>12872819301.1214</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12050.756</t>
+          <t>12955096134.8369</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16278.247</t>
+          <t>17545418211.2407</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16034.882</t>
+          <t>17215402698.7601</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16221.475</t>
+          <t>17372619309.4471</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>13938.726</t>
+          <t>14584988433.6887</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>14908.018</t>
+          <t>15872360179.2415</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14890.393</t>
+          <t>16098575265.1342</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>16443.074</t>
+          <t>17503197529.9514</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>17206.697</t>
+          <t>18411846814.5864</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>16758.855</t>
+          <t>17901595957.0092</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>17637.848</t>
+          <t>18747389205.9725</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>13480.09</t>
+          <t>14391079871.0613</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10924.604</t>
+          <t>11610088681.7831</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>14125.461</t>
+          <t>14812192589.9043</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>14218.061</t>
+          <t>14957264427.7096</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14084.651</t>
+          <t>14927929018.3627</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>13231.108</t>
+          <t>14010835050.919</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14005.955</t>
+          <t>14909136661.2436</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13631.556</t>
+          <t>14621425123.2015</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4809.668</t>
+          <t>5685727197.10292</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3750.433</t>
+          <t>4449490662.53845</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4033.841</t>
+          <t>4741161052.9765</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4209.051</t>
+          <t>4989427601.86334</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4502.84</t>
+          <t>5365901664.97403</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4143.609</t>
+          <t>4940994797.0098</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4293.354</t>
+          <t>5162015298.16883</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4066.706</t>
+          <t>4848747417.2342</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4150.354</t>
+          <t>4935386013.15534</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4043.466</t>
+          <t>4769958560.06604</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3981.681</t>
+          <t>4720571447.6805</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4090.241</t>
+          <t>4847936500.74692</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3539.566</t>
+          <t>4185986359.80727</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3809.934</t>
+          <t>4502914644.58803</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4152.836</t>
+          <t>4895554291.70103</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4231.61</t>
+          <t>5041129080.30852</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4284.661</t>
+          <t>5137334672.66185</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4116.434</t>
+          <t>4932022938.8693</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4129.686</t>
+          <t>4957088842.5258</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3895.95</t>
+          <t>4624569792.02901</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3791.597</t>
+          <t>4514884496.41789</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4862.151</t>
+          <t>5764657385.07529</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4684.657</t>
+          <t>5535973998.76722</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5409.103</t>
+          <t>6404258147.18354</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4975.931</t>
+          <t>5851513988.1227</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>5510.589</t>
+          <t>6539179421.47448</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4541.089</t>
+          <t>5410329763.14793</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13834.665</t>
+          <t>16527215322.8516</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6800.684</t>
+          <t>8195537499.49487</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9268.04</t>
+          <t>10955316320.4011</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7804.665</t>
+          <t>9231960897.08163</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8875.015</t>
+          <t>10680321292.5516</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8005.335</t>
+          <t>9546605129.57443</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8986.486</t>
+          <t>10689015537.4506</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9136.299</t>
+          <t>10807449360.3777</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8978.231</t>
+          <t>10480712980.9023</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10214.913</t>
+          <t>11958062455.3204</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11222.887</t>
+          <t>13060476666.9074</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11797.249</t>
+          <t>13792537064.1104</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>10732.519</t>
+          <t>12291014694.3356</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>9643.137</t>
+          <t>11162049386.1618</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>10482.475</t>
+          <t>12226184549.9706</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>9733.068</t>
+          <t>11401187835.1243</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>8351.358</t>
+          <t>9816484638.0919</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>10547.013</t>
+          <t>12538295484.0354</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>9459.078</t>
+          <t>11203821000.0318</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>8306.719</t>
+          <t>9756101857.02588</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>8645.696</t>
+          <t>10331064151.6905</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>10551.254</t>
+          <t>12513875027.5579</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>10116.186</t>
+          <t>11848537552.5843</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11768.09</t>
+          <t>13875974073.013</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9989.771</t>
+          <t>11697600588.4083</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11832.991</t>
+          <t>13994981012.4459</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>11766.75</t>
+          <t>14031523493.5452</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1196.665</t>
+          <t>1326190490.38306</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1040.344</t>
+          <t>1159094823.8967</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1186.33</t>
+          <t>1300400494.09145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1045.478</t>
+          <t>1152718023.2577</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1035.427</t>
+          <t>1150147205.68157</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1087.548</t>
+          <t>1198473346.21971</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>961.129</t>
+          <t>1075264350.1726</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>972.716</t>
+          <t>1067836317.02445</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>947.512</t>
+          <t>1045612701.95462</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1023.25</t>
+          <t>1134888558.37428</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1037.583</t>
+          <t>1139206260.29887</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1222.255</t>
+          <t>1337242339.6059</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1094.46</t>
+          <t>1204585607.86334</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1270.973</t>
+          <t>1416142077.98316</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1558.753</t>
+          <t>1728852436.92357</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1416.309</t>
+          <t>1586499497.67271</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1368.12</t>
+          <t>1548895971.54588</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1280.918</t>
+          <t>1442935471.41064</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1360.221</t>
+          <t>1537970077.94297</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1297.616</t>
+          <t>1483316071.23207</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1413.938</t>
+          <t>1611857198.32161</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1544.697</t>
+          <t>1758960637.60183</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1291.301</t>
+          <t>1476779827.44905</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1899.752</t>
+          <t>2150869109.47585</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2003.483</t>
+          <t>2256412751.23517</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2376.632</t>
+          <t>2680789603.30148</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1522.653</t>
+          <t>1722965421.57162</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>45516.028</t>
+          <t>46486019116.6534</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47226.566</t>
+          <t>47447109198.3566</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>43258.006</t>
+          <t>43668974143.5307</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45406.115</t>
+          <t>45968051452.0636</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>42584.906</t>
+          <t>43077647240.335</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>42741.506</t>
+          <t>43341436227.0178</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>43918.835</t>
+          <t>44412420632.218</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>41166.825</t>
+          <t>41724608749.8734</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>39785.736</t>
+          <t>40160205832.4738</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40129.511</t>
+          <t>40654587732.7074</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>44152.115</t>
+          <t>44493071452.7386</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>47514.94</t>
+          <t>48085998018.3413</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>45523.953</t>
+          <t>46027137119.4162</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>49105.215</t>
+          <t>49924813917.708</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>48194.888</t>
+          <t>49040847391.3027</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>50931.028</t>
+          <t>51937851417.7071</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>50172.364</t>
+          <t>51430829033.1814</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48990.243</t>
+          <t>50330605917.6151</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>50860.591</t>
+          <t>52199912291.8751</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>45834.49</t>
+          <t>46708037887.9216</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>41423.37</t>
+          <t>42125762472.9701</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>36834.488</t>
+          <t>37591298008.0277</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>39886.052</t>
+          <t>40765804768.2968</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>41877.759</t>
+          <t>42852926991.7336</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>36669.06</t>
+          <t>37467385388.1775</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>38923.361</t>
+          <t>39911215689.1054</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>41153.246</t>
+          <t>42361758284.719</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>109278.33</t>
+          <t>107521170128.009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11634.867</t>
+          <t>12565812061.7297</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9458.421</t>
+          <t>10255989872.1644</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10307.113</t>
+          <t>11184810776.278</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11343.188</t>
+          <t>12410080291.4961</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12146.273</t>
+          <t>13145056407.8043</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12867.996</t>
+          <t>13993100927.2131</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13234.271</t>
+          <t>14302493002.4927</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13588.637</t>
+          <t>14470158431.3952</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13869.618</t>
+          <t>14879944587.4623</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14413.766</t>
+          <t>15339793635.4607</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13550.335</t>
+          <t>14583034679.6431</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>14019.862</t>
+          <t>14784901147.843</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>14593.626</t>
+          <t>15594982083.2656</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>14523.908</t>
+          <t>15592997203.4528</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>13947.522</t>
+          <t>15238827792.9433</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>15674.634</t>
+          <t>17030750806.9187</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>16818.91</t>
+          <t>18363891424.1735</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>16049.824</t>
+          <t>17415077723.7868</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>15231.24</t>
+          <t>16485681867.6548</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>14793.005</t>
+          <t>16027084585.3584</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>16108.021</t>
+          <t>17522921414.4571</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>16229.398</t>
+          <t>17314434813.2546</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16404.771</t>
+          <t>17586158005.7895</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>16341.1</t>
+          <t>17481942081.6151</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17738.996</t>
+          <t>19006117581.4826</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>16419.304</t>
+          <t>17764861997.558</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>501846.797</t>
+          <t>486225640607.153</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>296166.251</t>
+          <t>285656363947.502</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>534517.628</t>
+          <t>520725392084.012</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>868788.565</t>
+          <t>852960666040.069</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>592987.93</t>
+          <t>579612905011.335</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>635696.029</t>
+          <t>623714486384.807</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>692342.323</t>
+          <t>679222138176.186</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>789540.412</t>
+          <t>771317284664.829</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>787846.99</t>
+          <t>766502591104.553</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>569039.494</t>
+          <t>551206205484.72</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>519687.461</t>
+          <t>502044474413.96</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>730890.17</t>
+          <t>704315107454.83</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>705893.701</t>
+          <t>674904768325.599</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>678621.328</t>
+          <t>652973533007.94</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>764589.97</t>
+          <t>735162029090.686</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>669921.76</t>
+          <t>643064339842.4</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>709055.95</t>
+          <t>681322999458.945</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>704839.754</t>
+          <t>682928634308.938</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>671460.132</t>
+          <t>647427866620.565</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>500895.612</t>
+          <t>488130228648.836</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>445712.076</t>
+          <t>433045901333.31</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>697030.275</t>
+          <t>665186966551.494</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>559591.695</t>
+          <t>547401746892.965</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>730782.193</t>
+          <t>699770430285.919</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>537107.389</t>
+          <t>520043517413.909</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>816537.361</t>
+          <t>780099783008.43</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>854400.571</t>
+          <t>816107336594.682</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>539.328</t>
+          <t>589104507.60973</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>553.603</t>
+          <t>601675218.852194</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>436.263</t>
+          <t>469949241.251025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>516.108</t>
+          <t>556296765.183439</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>522.79</t>
+          <t>572272606.572987</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>563.194</t>
+          <t>621223363.518547</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>481.307</t>
+          <t>533344713.654339</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>443.814</t>
+          <t>486165552.60562</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>476.372</t>
+          <t>522047595.09559</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>417.254</t>
+          <t>458185060.70964</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>408.148</t>
+          <t>452054318.862723</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>302.4</t>
+          <t>334847259.288668</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>271.019</t>
+          <t>297580852.540648</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>283.882</t>
+          <t>314073409.21233</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>396.073</t>
+          <t>438024275.029108</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>316.809</t>
+          <t>357862393.393087</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>234.035</t>
+          <t>262075487.553218</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>255.004</t>
+          <t>291230051.763959</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>255.804</t>
+          <t>293931972.379671</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>211.139</t>
+          <t>241061233.929738</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>236.619</t>
+          <t>267661282.633232</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>261.887</t>
+          <t>297608977.855198</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>253.95</t>
+          <t>284587797.129412</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>249.506</t>
+          <t>285438427.584296</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>277.805</t>
+          <t>314195276.701261</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>282.376</t>
+          <t>320021814.061232</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>131.496</t>
+          <t>139729384.35506</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3561.756</t>
+          <t>4047461835.92609</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2324.059</t>
+          <t>2652629505.4867</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2732.755</t>
+          <t>3078571423.76889</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2296.968</t>
+          <t>2603947258.28856</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2348.594</t>
+          <t>2643725407.03056</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2223.896</t>
+          <t>2505402294.24144</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2390.163</t>
+          <t>2693748380.27588</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2253.308</t>
+          <t>2597973021.33514</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2258.27</t>
+          <t>2585472246.885</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2630.26</t>
+          <t>2970853366.24074</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2935.811</t>
+          <t>3330102486.28807</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3309.784</t>
+          <t>3787683000.44927</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3162.439</t>
+          <t>3590862257.49047</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3006.041</t>
+          <t>3451027489.58701</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2772.931</t>
+          <t>3109979000.03755</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2937.932</t>
+          <t>3339741529.15133</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2585.315</t>
+          <t>2954756012.95388</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2825.325</t>
+          <t>3215126579.33335</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2718.065</t>
+          <t>3098959950.23908</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2676.899</t>
+          <t>3014108505.01965</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3127.488</t>
+          <t>3509889930.47028</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>3352.428</t>
+          <t>3753393093.63725</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2924.883</t>
+          <t>3238488611.50341</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3229.594</t>
+          <t>3601554048.11415</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>3848.752</t>
+          <t>4272502707.00078</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>4233.489</t>
+          <t>4704917955.09319</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>4102.771</t>
+          <t>4594604481.29168</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>49368.581</t>
+          <t>55757332973.6843</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48178.39</t>
+          <t>53333180941.8206</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>45492.746</t>
+          <t>49633456810.623</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44765.368</t>
+          <t>49152812210.2428</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45426.647</t>
+          <t>50176303569.1104</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>46044.57</t>
+          <t>50675036334.7015</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>41821.133</t>
+          <t>46016630011.2001</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>40350.635</t>
+          <t>44234504527.9877</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>51302.498</t>
+          <t>55516716440.5853</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>43904.049</t>
+          <t>48112099016.0297</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>42608.405</t>
+          <t>46066979706.2166</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>43541.586</t>
+          <t>47333080228.5932</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>39093.306</t>
+          <t>42193047493.1759</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>41518.779</t>
+          <t>45148129979.7592</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>40963.15</t>
+          <t>44095328422.0827</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>42026.291</t>
+          <t>45334015603.1312</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>39668.762</t>
+          <t>43046667115.204</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>39031.491</t>
+          <t>42551530258.3838</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>40298.963</t>
+          <t>43974302957.3872</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>41632.614</t>
+          <t>44861799512.0023</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>36148.869</t>
+          <t>38634907256.1261</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>39851.946</t>
+          <t>42706392734.1503</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>41976.602</t>
+          <t>44905255492.7247</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>43128.102</t>
+          <t>45984120798.6186</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>40944.263</t>
+          <t>43557536660.2806</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>48112.064</t>
+          <t>51767331313.4706</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>45923.821</t>
+          <t>49515983408.9928</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4102.135</t>
+          <t>4750945569.38142</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3271.093</t>
+          <t>3745419257.85153</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3140.977</t>
+          <t>3494090385.99184</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2768.512</t>
+          <t>3106573424.30458</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3126.27</t>
+          <t>3468273690.67135</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4009.67</t>
+          <t>4409582392.21969</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3994.488</t>
+          <t>4394606235.88136</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4106.462</t>
+          <t>4494720214.14895</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4171.182</t>
+          <t>4511692541.1622</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3856.362</t>
+          <t>4220200512.4629</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4135.36</t>
+          <t>4479153238.56729</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4051.702</t>
+          <t>4395892625.98453</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3647.84</t>
+          <t>3933665296.12482</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3885.525</t>
+          <t>4344828492.27929</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3756.789</t>
+          <t>4169526375.38894</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>3357.834</t>
+          <t>3704786178.25984</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3675.099</t>
+          <t>4123368355.09031</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3446.476</t>
+          <t>3826359850.65624</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4056.014</t>
+          <t>4486373401.66431</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3628.811</t>
+          <t>3899094121.75341</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3473.916</t>
+          <t>3738258279.04179</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>3613.965</t>
+          <t>3910061966.46955</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>3518.306</t>
+          <t>3775338541.88911</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4030.027</t>
+          <t>4307642113.76112</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>3190.265</t>
+          <t>3419979402.46498</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>3741.769</t>
+          <t>4018141176.37169</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>3657.283</t>
+          <t>3983946062.55775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>36246.816</t>
+          <t>40552011884.0923</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12659.855</t>
+          <t>14249897135.2749</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12910.936</t>
+          <t>14320917773.9035</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14082.993</t>
+          <t>15682759182.4646</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15182.606</t>
+          <t>17020166003.8328</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16218.612</t>
+          <t>18178755848.7139</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17411.675</t>
+          <t>19496204471.1624</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18350.658</t>
+          <t>20511058260.0363</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17076.078</t>
+          <t>18830282570.9857</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>18933.713</t>
+          <t>20961125395.9382</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20274.964</t>
+          <t>22386768936.8628</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>20511.998</t>
+          <t>22786158208.5214</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>19952.021</t>
+          <t>21758303098.7674</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>22119.539</t>
+          <t>24238384480.9071</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>18007.504</t>
+          <t>19675451602.0103</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17015.013</t>
+          <t>18575127788.7111</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>16691.301</t>
+          <t>18377704575.5618</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>16644.391</t>
+          <t>18313009053.5919</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>16060.289</t>
+          <t>17778220977.3555</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15067.852</t>
+          <t>16199786484.8815</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>14559.804</t>
+          <t>15603697815.7647</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>16051.994</t>
+          <t>17022675765.5568</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>18485.044</t>
+          <t>19197248427.7687</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>23477.017</t>
+          <t>24390922056.723</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>20875.061</t>
+          <t>21598153544.6212</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>22424.474</t>
+          <t>23244530130.5291</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>23578.046</t>
+          <t>24688544924.9613</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>784.532</t>
+          <t>898016872.75452</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>765.555</t>
+          <t>857436680.965258</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>794.045</t>
+          <t>819274106.22806</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>739.006</t>
+          <t>778116210.396263</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>655.705</t>
+          <t>697590602.729899</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>659.458</t>
+          <t>731632982.283988</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>583.299</t>
+          <t>635565505.543878</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>742.848</t>
+          <t>794648842.967498</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>793.83</t>
+          <t>843396463.376348</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>448.939</t>
+          <t>501489981.694448</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>513.617</t>
+          <t>574430606.222263</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>908.137</t>
+          <t>951352748.328834</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>761.536</t>
+          <t>820333389.950043</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>997.909</t>
+          <t>1056814753.44278</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1019.11</t>
+          <t>1056047763.0686</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1052.06</t>
+          <t>1097259625.36654</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>702.468</t>
+          <t>755602354.228377</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1064.891</t>
+          <t>1097275485.35982</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>948.819</t>
+          <t>977345349.104979</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>737.737</t>
+          <t>768464806.716001</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>572.38</t>
+          <t>603699241.722142</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>816.382</t>
+          <t>843421663.979202</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>766.882</t>
+          <t>791351717.657795</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>828.111</t>
+          <t>859299636.090849</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>762.342</t>
+          <t>791379276.199803</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>943.326</t>
+          <t>982569998.502914</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>626.039</t>
+          <t>670929493.363358</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3554.589</t>
+          <t>3784442134.59048</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2763.73</t>
+          <t>2830719027.56965</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2722.286</t>
+          <t>2767993353.87707</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2825.868</t>
+          <t>2896261755.69812</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2588.904</t>
+          <t>2755617117.55259</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2776.175</t>
+          <t>2953964996.08203</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2825.548</t>
+          <t>2981660609.90676</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2662.783</t>
+          <t>2788710871.47825</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2667.485</t>
+          <t>2784054043.87952</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2590.681</t>
+          <t>2770922487.57105</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2859.866</t>
+          <t>2971661948.23125</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2822.422</t>
+          <t>2935289334.67482</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2521.736</t>
+          <t>2622300532.84859</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3209.215</t>
+          <t>3371829334.32091</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2714.739</t>
+          <t>2821327445.18116</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2594.7</t>
+          <t>2664603017.98346</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2524.335</t>
+          <t>2666931028.99842</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2627.537</t>
+          <t>2689741236.69784</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2614.649</t>
+          <t>2701586084.34522</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2415.593</t>
+          <t>2470064952.72271</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2179.469</t>
+          <t>2250635294.14369</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2248.958</t>
+          <t>2313468251.97418</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2054.334</t>
+          <t>2109522302.8207</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2942.053</t>
+          <t>2929386694.73906</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2387.071</t>
+          <t>2384442662.41401</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2743.467</t>
+          <t>2741908729.78966</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2943.33</t>
+          <t>3016513955.78253</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>70437.301</t>
+          <t>70266589924.2966</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36035.311</t>
+          <t>38493447695.9485</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34451.232</t>
+          <t>35795994168.2998</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32410.901</t>
+          <t>34289642996.7655</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>36058.133</t>
+          <t>38433918692.4781</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>35722.391</t>
+          <t>38179179684.9854</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>36126.455</t>
+          <t>38563023754.8732</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33982.804</t>
+          <t>36392480261.0316</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>33553.376</t>
+          <t>35640424235.042</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>35067.023</t>
+          <t>37412867051.9063</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>36180.864</t>
+          <t>38414838413.6429</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>33661.461</t>
+          <t>35905177803.1894</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>35435.735</t>
+          <t>37304980222.0248</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>38410.609</t>
+          <t>39139841340.4862</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>33108.365</t>
+          <t>34103566955.5056</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>34159.04</t>
+          <t>35533476157.5927</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>34640.83</t>
+          <t>35831740720.1429</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>37345.817</t>
+          <t>38515694404.2719</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>34776.472</t>
+          <t>36289486565.0208</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>39050.598</t>
+          <t>38171462993.5171</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>35551.634</t>
+          <t>35009824358.7663</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>41621.736</t>
+          <t>40391209902.8944</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>41316.644</t>
+          <t>38588264255.6038</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>46775.95</t>
+          <t>44018078249.711</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>45006.014</t>
+          <t>42376203954.5731</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>55137.084</t>
+          <t>50637112097.3146</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>50504.48</t>
+          <t>47244828718.7932</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>34968.251</t>
+          <t>41595798093.9035</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29985.484</t>
+          <t>34938272763.761</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28833.982</t>
+          <t>33351088863.6584</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31367.38</t>
+          <t>36591701295.384</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>35365.156</t>
+          <t>41747982875.4389</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>38357.804</t>
+          <t>45111359097.5004</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>37091.919</t>
+          <t>43350517174.6523</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38847.786</t>
+          <t>45816035830.3721</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>39892.458</t>
+          <t>46747816708.3284</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>44320.376</t>
+          <t>52144664154.4622</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>43076.897</t>
+          <t>50155428808.4697</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>44931.181</t>
+          <t>52754987228.5081</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>38341.614</t>
+          <t>44344761823.4296</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>39713.778</t>
+          <t>46329237565.7157</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>36103.425</t>
+          <t>41913181085.4231</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>36092.031</t>
+          <t>42087843273.158</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>33265.241</t>
+          <t>38877622167.3326</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>31610.09</t>
+          <t>37523781983.744</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>31129.257</t>
+          <t>36488592417.3741</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>35403.837</t>
+          <t>41385703494.1755</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>37079.523</t>
+          <t>43381632791.4176</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>35907.765</t>
+          <t>41719101862.1539</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>32059.612</t>
+          <t>37127839188.5148</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>34380.379</t>
+          <t>40340959979.1045</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>34878.465</t>
+          <t>40885563934.3277</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>36781.798</t>
+          <t>43322329035.7704</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>38761.8</t>
+          <t>45935738384.2046</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2476.565</t>
+          <t>2872665613.50762</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3655.6</t>
+          <t>4152667842.26052</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3058.751</t>
+          <t>3426556737.55929</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3087.762</t>
+          <t>3429344330.2115</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2781.529</t>
+          <t>3106886575.51941</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3540.139</t>
+          <t>3936572461.68847</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3258.784</t>
+          <t>3604979024.56311</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3628.53</t>
+          <t>3998774504.21976</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3763.262</t>
+          <t>4029628899.37897</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4017.63</t>
+          <t>4384664624.46862</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3976.662</t>
+          <t>4154792047.88514</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3964.053</t>
+          <t>4148722462.91001</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3804.511</t>
+          <t>4067020187.91803</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4106.459</t>
+          <t>4277228063.60452</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3844.927</t>
+          <t>3926894461.56329</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>3184.482</t>
+          <t>3494981702.6059</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2813.494</t>
+          <t>3018960503.55878</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2441.286</t>
+          <t>2657280321.21106</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2438.23</t>
+          <t>2593891340.31417</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2069.099</t>
+          <t>2181679132.32386</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1976.432</t>
+          <t>2066405604.1373</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>1896.421</t>
+          <t>1987869725.42042</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>1846.431</t>
+          <t>1905616450.53478</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1934.412</t>
+          <t>1970653752.30582</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1904.387</t>
+          <t>1928062440.65759</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>1797.151</t>
+          <t>1798482745.25049</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1962.165</t>
+          <t>1995414483.7851</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3465.501</t>
+          <t>3757200156.51844</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2645.933</t>
+          <t>3144826093.13967</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2367.264</t>
+          <t>2674085192.0245</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2488.202</t>
+          <t>2852248954.61968</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2539.219</t>
+          <t>2929445310.62033</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2502.38</t>
+          <t>2842838309.32843</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2697.74</t>
+          <t>3136754208.02288</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2514.747</t>
+          <t>2833455116.7512</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2811.638</t>
+          <t>3196803880.38325</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2994.729</t>
+          <t>3431856990.55023</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2839.308</t>
+          <t>3274821773.8631</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2562.209</t>
+          <t>2906702689.31729</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2567.474</t>
+          <t>2851672660.8222</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2840.99</t>
+          <t>3215845860.64325</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2515.667</t>
+          <t>2770750907.45892</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2114.288</t>
+          <t>2336990819.53349</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2334.537</t>
+          <t>2556466892.4045</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2099.794</t>
+          <t>2276082741.14351</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2019.154</t>
+          <t>2226792757.17743</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2146.843</t>
+          <t>2316742510.82666</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2131.033</t>
+          <t>2334647839.44778</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2262.37</t>
+          <t>2434726706.61303</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2365.077</t>
+          <t>2502157823.33006</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2498.11</t>
+          <t>2715064923.33254</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2692.519</t>
+          <t>2810980490.09173</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>3141.977</t>
+          <t>3209227272.43524</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2909.885</t>
+          <t>3090356482.54149</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>955790.142</t>
+          <t>956882244642.34</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>389606.967</t>
+          <t>388686069464.542</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>386480.181</t>
+          <t>385597089715.633</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>419964.887</t>
+          <t>419429362672.206</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>432250.882</t>
+          <t>431805008083.28</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>433783.337</t>
+          <t>433143217624.679</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>465208.867</t>
+          <t>464120372037.605</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>456867.403</t>
+          <t>456129939563.79</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>438027.184</t>
+          <t>436660126357.937</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>501256.555</t>
+          <t>500190227850.466</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>493655.839</t>
+          <t>492846134947.43</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>473103.076</t>
+          <t>472381085881.78</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>478877.611</t>
+          <t>477785197483.266</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>456038.152</t>
+          <t>455607922425.081</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>469208.271</t>
+          <t>469003519274.958</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>438766.42</t>
+          <t>439134980478.923</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>434209.464</t>
+          <t>435301201921.312</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>407888.851</t>
+          <t>409252916742.601</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>386735.912</t>
+          <t>388172173554.958</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>434753.705</t>
+          <t>437540653396.04</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>466472.929</t>
+          <t>469064928585.469</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>559129.552</t>
+          <t>561746091243.924</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>594921.767</t>
+          <t>597662642900.567</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>625073.416</t>
+          <t>628149987256.694</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>621300.704</t>
+          <t>623070105670.614</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>718561.134</t>
+          <t>721022005155.556</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>773631.583</t>
+          <t>775790923836.605</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>77019.678</t>
+          <t>82673637731.9589</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29593.099</t>
+          <t>31859534377.5953</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31219.992</t>
+          <t>33617196778.6392</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20965.016</t>
+          <t>22997540796.6766</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>26247.402</t>
+          <t>28247607176.96</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>31943.919</t>
+          <t>34139264865.3433</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29438.396</t>
+          <t>31586500954.4301</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30072.574</t>
+          <t>32529893177.084</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28279.497</t>
+          <t>31253579696.7359</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>37835.991</t>
+          <t>40528754287.8399</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>39308.054</t>
+          <t>42788542267.3231</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>38252.403</t>
+          <t>42111143739.2909</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>38667.411</t>
+          <t>42092327275.2458</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>41539.573</t>
+          <t>44857653298.6015</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>40593.022</t>
+          <t>45044112911.0295</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>43806.459</t>
+          <t>48048363096.9515</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>40707.363</t>
+          <t>44720839173.8252</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>42067.203</t>
+          <t>46054175456.6114</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>41010.112</t>
+          <t>44295651035.6951</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>38641.848</t>
+          <t>42438227753.0193</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>42851.005</t>
+          <t>46338366995.795</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>57600.527</t>
+          <t>61912797441.1127</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>58629.818</t>
+          <t>62690674108.5169</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>62887.281</t>
+          <t>67495610783.134</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>62070.3</t>
+          <t>66387432172.9175</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>70799.653</t>
+          <t>76017407907.734</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>73082.66</t>
+          <t>78635133835.7937</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1561.965</t>
+          <t>1744616044.17095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1433.131</t>
+          <t>1599580738.32057</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1480.423</t>
+          <t>1600614834.00857</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1614.055</t>
+          <t>1734589523.10794</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1979.272</t>
+          <t>2125985600.38444</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2191.536</t>
+          <t>2338253350.85423</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2251.69</t>
+          <t>2430833376.19845</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1731.618</t>
+          <t>1853791291.60175</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1835.275</t>
+          <t>1937586953.4156</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2181.589</t>
+          <t>2293476524.31854</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2363.852</t>
+          <t>2527715439.22182</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2272.277</t>
+          <t>2430708275.33551</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2059.12</t>
+          <t>2177353779.34404</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1964.06</t>
+          <t>2097499372.10171</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2463.987</t>
+          <t>2600836162.43788</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1893.092</t>
+          <t>1966309123.98858</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2113.604</t>
+          <t>2194838553.97876</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1781.085</t>
+          <t>1902482588.73317</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2255.156</t>
+          <t>2430984748.37875</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2057.855</t>
+          <t>2149819475.08175</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2731.562</t>
+          <t>2816821362.18799</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>3740.267</t>
+          <t>3824225725.09102</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2963.352</t>
+          <t>2984211376.77299</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2879.815</t>
+          <t>2941219194.96519</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>3265.507</t>
+          <t>3257941543.12391</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>3921.026</t>
+          <t>3900213802.95099</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3967.419</t>
+          <t>3992776943.3414</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>25954.59</t>
+          <t>30486604386.5262</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27016.58</t>
+          <t>31061539684.1251</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23171.158</t>
+          <t>26717419800.762</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>22484.522</t>
+          <t>25906966831.2065</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26763.242</t>
+          <t>31053112032.87</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27452.199</t>
+          <t>31375106425.9737</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25650.581</t>
+          <t>29545314053.6766</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25909.839</t>
+          <t>29554916577.7859</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26222.597</t>
+          <t>29544239760.7449</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28326.072</t>
+          <t>32265939601.0886</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>28008.571</t>
+          <t>31749945332.7764</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>27719.397</t>
+          <t>31685932194.084</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>24928.673</t>
+          <t>28168333791.0576</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>24876.808</t>
+          <t>28438337195.2406</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>24215.901</t>
+          <t>27563485880.8435</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>24983.284</t>
+          <t>28547587269.4145</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>23683.368</t>
+          <t>27082040970.5207</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>22496.815</t>
+          <t>25944107304.8473</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>22294.838</t>
+          <t>25801789535.2421</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>20043.579</t>
+          <t>22706892295.9782</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>18705.324</t>
+          <t>21179382192.3163</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>18994.939</t>
+          <t>21501576754.5047</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>18581.411</t>
+          <t>20869065991.648</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19747.7</t>
+          <t>22366149550.3354</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>18608.718</t>
+          <t>21018650297.171</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19893.002</t>
+          <t>22530585878.8392</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>19580.417</t>
+          <t>22265433076.0142</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>128925.79</t>
+          <t>147702787366.353</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>89474.902</t>
+          <t>98525701800.3275</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79508.888</t>
+          <t>85675997860.2349</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>79841.785</t>
+          <t>86272806384.8296</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>83922.642</t>
+          <t>91959468000.2643</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>100369.164</t>
+          <t>109813709965.54</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>96256.855</t>
+          <t>106738675670.212</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>82436.79</t>
+          <t>90629298509.4434</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>76977.033</t>
+          <t>82382727904.3439</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>79819.335</t>
+          <t>87139822028.9441</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>78173.773</t>
+          <t>84862210515.1992</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>73967.196</t>
+          <t>80197338004.9139</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>60134.445</t>
+          <t>62477873822.2675</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>62931.712</t>
+          <t>68442174205.2681</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>55587.168</t>
+          <t>60818084026.1971</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>61445.076</t>
+          <t>67467828822.6489</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>58702.035</t>
+          <t>64784812626.7189</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>63071.358</t>
+          <t>70478639138.6506</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>57108.182</t>
+          <t>63064885042.141</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>55847.248</t>
+          <t>62137684954.4453</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>50012.506</t>
+          <t>56131113172.2563</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>48448.786</t>
+          <t>53476323925.4137</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>45280.996</t>
+          <t>50240204981.6393</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>51460.943</t>
+          <t>57174824248.6467</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>49978.809</t>
+          <t>55339691820.7626</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>52777.098</t>
+          <t>58810105567.3047</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>61949.078</t>
+          <t>70549041813.3058</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>39826.693</t>
+          <t>44064772336.5896</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20991.032</t>
+          <t>22954195897.4961</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21840.702</t>
+          <t>23546813635.3446</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16630.501</t>
+          <t>18236858597.4496</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17624.302</t>
+          <t>19492063554.0828</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19344.039</t>
+          <t>21237471245.3093</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20246.446</t>
+          <t>22222494262.9665</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20892.832</t>
+          <t>22839094915.6499</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22062.189</t>
+          <t>23547670309.3092</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23852.061</t>
+          <t>25957193304.7733</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23901.394</t>
+          <t>26040197509.7438</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>27740.942</t>
+          <t>30064875269.8189</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>22196.979</t>
+          <t>23289278770.7896</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>23436.388</t>
+          <t>25426841804.1308</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>21285.957</t>
+          <t>23219321925.8053</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>20380.849</t>
+          <t>22288161624.081</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>20876.142</t>
+          <t>22852926204.2908</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>23846.7</t>
+          <t>26294982997.7901</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24125.873</t>
+          <t>26612280782.9287</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>22021.754</t>
+          <t>24294639759.4208</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>17743.26</t>
+          <t>19278957104.1643</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>22709.797</t>
+          <t>24860726924.9939</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>24381.239</t>
+          <t>26330170027.8482</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20635.513</t>
+          <t>22496942182.9539</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>22820.013</t>
+          <t>24654174745.6673</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>22331.872</t>
+          <t>24285926091.5296</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>22152.736</t>
+          <t>24247427125.9333</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1112.542</t>
+          <t>1395999344.96201</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>767.044</t>
+          <t>872793488.105329</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1165.963</t>
+          <t>1388810617.46191</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1072.971</t>
+          <t>1249422324.04084</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1138.476</t>
+          <t>1337415104.64125</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1229.17</t>
+          <t>1464079619.54328</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1005.072</t>
+          <t>1194335577.65143</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1164.353</t>
+          <t>1361492786.51447</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>969.461</t>
+          <t>1129442017.31342</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1072.732</t>
+          <t>1238742774.56714</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1050.52</t>
+          <t>1221730712.22216</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1083.028</t>
+          <t>1263096074.22395</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>966.45</t>
+          <t>1111356945.22311</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1111.193</t>
+          <t>1300616436.28522</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1009.857</t>
+          <t>1151493696.56728</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>896.972</t>
+          <t>1042552793.65929</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>979.985</t>
+          <t>1134036730.56365</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>981.37</t>
+          <t>1143211985.94751</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>864.382</t>
+          <t>995920457.062872</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>956.056</t>
+          <t>1092552502.82806</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>955.692</t>
+          <t>1098803129.75399</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1001.166</t>
+          <t>1151525070.39055</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1040.982</t>
+          <t>1198673693.95455</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1357.562</t>
+          <t>1573659178.86076</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1223.502</t>
+          <t>1416704764.28567</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1321.49</t>
+          <t>1536426430.54431</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1020.772</t>
+          <t>1172510583.13444</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>242.034</t>
+          <t>271258051.988917</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>402.705</t>
+          <t>466033517.383414</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>545.8</t>
+          <t>632017773.737675</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>787.648</t>
+          <t>912828688.794501</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>801.377</t>
+          <t>934645136.677316</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1116.813</t>
+          <t>1306483569.56179</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1582.462</t>
+          <t>1856941191.44456</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1379.75</t>
+          <t>1609462747.72973</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>969.444</t>
+          <t>1137124551.30167</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1102.175</t>
+          <t>1277782556.79004</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1417.227</t>
+          <t>1629960084.95443</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1587.496</t>
+          <t>1833394399.99967</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1328.998</t>
+          <t>1519630625.39782</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1824.281</t>
+          <t>2099793016.27966</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1660.801</t>
+          <t>1927373843.96991</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1850.309</t>
+          <t>2140136717.24717</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1464.824</t>
+          <t>1718544378.53581</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2094.203</t>
+          <t>2442357696.17363</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2227.232</t>
+          <t>2619629701.55393</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2653.175</t>
+          <t>3092025885.87652</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2486.097</t>
+          <t>2926245213.49932</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2614.178</t>
+          <t>3042382891.6121</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2756.408</t>
+          <t>3188544386.98983</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3619.127</t>
+          <t>4192924705.59033</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>3054.713</t>
+          <t>3538849511.06103</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>3431.323</t>
+          <t>3982611469.58869</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3502.325</t>
+          <t>4083146058.04676</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>912.575</t>
+          <t>1006405425.60579</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>671.541</t>
+          <t>709875680.474588</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>726.174</t>
+          <t>790936112.842737</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>706.762</t>
+          <t>782108841.597898</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>770.572</t>
+          <t>864017215.566572</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>887.92</t>
+          <t>1023029744.01071</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>877.911</t>
+          <t>1005166384.67748</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>957.03</t>
+          <t>1087465108.5969</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>677.519</t>
+          <t>761657184.672567</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>503.818</t>
+          <t>565064723.249503</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>597.033</t>
+          <t>670174653.363282</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>899.954</t>
+          <t>993201542.395606</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>886.897</t>
+          <t>984169363.559524</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>797.721</t>
+          <t>898097569.990835</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>592.165</t>
+          <t>666979616.196297</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>503.502</t>
+          <t>568612642.6937</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>576.789</t>
+          <t>673720379.163425</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>516.818</t>
+          <t>604748042.278389</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>557.014</t>
+          <t>632305896.532793</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>492.342</t>
+          <t>564646461.69381</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>566.35</t>
+          <t>653022810.869718</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>449.942</t>
+          <t>512079058.947308</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>558.554</t>
+          <t>647286097.158924</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>649.255</t>
+          <t>740909095.252167</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>641.469</t>
+          <t>733374253.942806</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>653.027</t>
+          <t>757315570.150955</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>524.11</t>
+          <t>589070098.777389</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>29520.744</t>
+          <t>30097432618.139</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15304.991</t>
+          <t>15452733975.1805</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16085.851</t>
+          <t>16251505783.1797</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>19393.05</t>
+          <t>19576148988.6894</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17994.155</t>
+          <t>18248517136.7634</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16989.706</t>
+          <t>17309256800.3623</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16319.494</t>
+          <t>16724768870.4168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16540.653</t>
+          <t>16995260217.2002</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15826.162</t>
+          <t>16148288134.8612</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>15202.963</t>
+          <t>15611070721.7879</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15789.959</t>
+          <t>16231230802.0837</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15431.104</t>
+          <t>15855159441.148</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>14636.511</t>
+          <t>14964772634.387</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>14912.639</t>
+          <t>15358329336.856</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13436.906</t>
+          <t>13766358570.3633</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>13109.646</t>
+          <t>13466507413.941</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13754.038</t>
+          <t>14129544131.0916</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>12501.721</t>
+          <t>12845430472.9965</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>12058.044</t>
+          <t>12325394183.4743</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>11824.751</t>
+          <t>12017667520.6273</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>13811.36</t>
+          <t>14137322249.8402</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>11096.254</t>
+          <t>11396310066.2123</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>10518.313</t>
+          <t>10698309835.0953</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10742.542</t>
+          <t>10897525413.3173</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>12019.076</t>
+          <t>12251150665.3009</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12709.555</t>
+          <t>12961580584.8441</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>10774.418</t>
+          <t>11042110743.5489</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>154.186</t>
+          <t>173255313.785672</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>227.176</t>
+          <t>266494542.313819</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>144.658</t>
+          <t>167702366.600428</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>167.642</t>
+          <t>193431717.829168</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>215.094</t>
+          <t>255710530.206228</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>183.729</t>
+          <t>215746071.842264</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>211.518</t>
+          <t>248341234.383749</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>192.245</t>
+          <t>228088127.426741</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>259.454</t>
+          <t>298766900.298464</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>173.593</t>
+          <t>202317205.428719</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>196.03</t>
+          <t>227320333.181188</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>218.567</t>
+          <t>256144964.105792</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>161.67</t>
+          <t>193626442.028067</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>202.646</t>
+          <t>240690509.594076</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>325.879</t>
+          <t>383770872.791906</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>251.972</t>
+          <t>296115765.817881</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>183.524</t>
+          <t>216215040.529837</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>179.682</t>
+          <t>215382317.30849</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>201728206.258411</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>171.758</t>
+          <t>203872368.239288</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>159.159</t>
+          <t>188931407.891709</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>255.018</t>
+          <t>297723646.532263</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>300.751</t>
+          <t>355979668.354571</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>265.35</t>
+          <t>309731586.425874</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>190.783</t>
+          <t>221978149.893217</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>182.455</t>
+          <t>213359963.947995</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>247.2</t>
+          <t>291087973.115535</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11368.223</t>
+          <t>13741468298.1349</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14441.023</t>
+          <t>16587405340.64</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12464.484</t>
+          <t>14289840010.8403</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13955.839</t>
+          <t>16016239648.524</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15330.975</t>
+          <t>17736600355.4858</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>16350.819</t>
+          <t>18912978370.6802</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16500.791</t>
+          <t>19047967832.0076</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17750.707</t>
+          <t>20379466220.2697</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17046.35</t>
+          <t>19381406228.6061</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16867.207</t>
+          <t>19308998965.2146</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>15918.271</t>
+          <t>18213092714.938</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>16564.709</t>
+          <t>19177176051.2055</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>13046.946</t>
+          <t>14983891133.5133</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>14927.677</t>
+          <t>17369660036.6993</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17682.971</t>
+          <t>20316289761.5645</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>17292.353</t>
+          <t>20075343949.9406</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13042.42</t>
+          <t>15302068286.0414</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15485.201</t>
+          <t>18107459450.2409</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>15148.756</t>
+          <t>17705827858.7522</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>16301.405</t>
+          <t>18883796437.9389</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>17241.172</t>
+          <t>19951659428.3827</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>17280.002</t>
+          <t>19904352366.5566</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>18201.712</t>
+          <t>20946732293.1328</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19156.412</t>
+          <t>22083294790.741</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>19701.237</t>
+          <t>22644396656.5016</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>23122.908</t>
+          <t>26646241215.4235</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>23851.196</t>
+          <t>27500661250.3238</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9798.675</t>
+          <t>10459128483.1375</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12132.55</t>
+          <t>13674596676.0515</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10598.05</t>
+          <t>11590538981.2085</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9983.907</t>
+          <t>10872306060.449</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9613.877</t>
+          <t>10573683291.7319</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9573.26</t>
+          <t>10616673765.9977</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9566.698</t>
+          <t>10629637140.1993</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8590.976</t>
+          <t>9581305172.82889</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7792.839</t>
+          <t>8606486165.11677</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6731.632</t>
+          <t>7507541571.72198</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7521.258</t>
+          <t>8327981221.95057</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7580.94</t>
+          <t>8439594657.77537</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>7820.775</t>
+          <t>8647342221.2894</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>9797.03</t>
+          <t>10926316645.6717</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>8281.739</t>
+          <t>9191952981.1291</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>8457.785</t>
+          <t>9433634049.37676</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>7970.451</t>
+          <t>9023765208.36956</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>8389.584</t>
+          <t>9494230793.36098</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>8559.518</t>
+          <t>9675828266.44453</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>8224.183</t>
+          <t>9260090351.71051</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>8292.897</t>
+          <t>9451033052.55154</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>7578.292</t>
+          <t>8532585568.15558</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>9631.004</t>
+          <t>10829324768.5357</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9370.688</t>
+          <t>10616342141.357</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>9247.179</t>
+          <t>10403786587.4047</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>9787.407</t>
+          <t>11286569097.2428</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>11403.567</t>
+          <t>12943863695.9478</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4873.35</t>
+          <t>6153083346.71474</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3945.86</t>
+          <t>4493684709.17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3532.208</t>
+          <t>3982428995.26143</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3636.159</t>
+          <t>4127160731.92118</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4082.524</t>
+          <t>4709112245.34831</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4402.576</t>
+          <t>5103827330.65177</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4435.165</t>
+          <t>5181973021.11103</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4329.652</t>
+          <t>5041573848.53629</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4237.536</t>
+          <t>4909514784.49955</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4315.502</t>
+          <t>5037937622.95861</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4225.057</t>
+          <t>4920135963.88062</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4366.393</t>
+          <t>5106063175.58602</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>4244.182</t>
+          <t>4921340323.73292</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>4524.253</t>
+          <t>5277325428.2076</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4280.651</t>
+          <t>4998347201.19533</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>3964.879</t>
+          <t>4648297582.11871</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>3997.891</t>
+          <t>4660327334.72892</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3712.624</t>
+          <t>4361473929.2841</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3794.717</t>
+          <t>4514884404.60642</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3312.462</t>
+          <t>3910622423.25341</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>3085.772</t>
+          <t>3605978695.24174</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>3249.068</t>
+          <t>3805994811.72274</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>3453.351</t>
+          <t>4035911392.87343</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>3483.714</t>
+          <t>4042845426.74944</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>3382.353</t>
+          <t>3988178798.48623</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>3633.455</t>
+          <t>4328277518.52398</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>3457.944</t>
+          <t>4070730377.7732</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5448.904</t>
+          <t>5527257220.39992</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5166.819</t>
+          <t>5265103592.53946</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5838.352</t>
+          <t>5982190373.78242</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6307.181</t>
+          <t>6463578405.47668</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6263.033</t>
+          <t>6432870433.51661</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7010.56</t>
+          <t>7244107961.98313</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6406.548</t>
+          <t>6642724227.81895</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6553.192</t>
+          <t>6772214889.78463</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5496.007</t>
+          <t>5777618218.24519</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5119.607</t>
+          <t>5332723682.70312</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5476.217</t>
+          <t>5706317356.87952</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>5244.851</t>
+          <t>5491950987.28586</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>5518.146</t>
+          <t>5841193137.53389</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6068.277</t>
+          <t>6391718774.5562</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4796.6</t>
+          <t>5115192774.09916</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>4709.416</t>
+          <t>5024157394.99339</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>4187.141</t>
+          <t>4443275386.80377</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>4662.913</t>
+          <t>4980309920.04942</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>4128.537</t>
+          <t>4402553817.14132</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>4259.768</t>
+          <t>4582424198.75689</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>3790.84</t>
+          <t>4128052655.61438</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>3585.29</t>
+          <t>3895365505.22111</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>4620.366</t>
+          <t>4991488844.61485</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>4964.842</t>
+          <t>5447929140.61737</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>4822.245</t>
+          <t>5301752886.98409</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>6216.183</t>
+          <t>6834713826.24598</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>5606.091</t>
+          <t>6045419114.5706</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>64854.462</t>
+          <t>73861778598.58</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>32815.193</t>
+          <t>31951036474.2561</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48096.999</t>
+          <t>50846821125.3572</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>40604.44</t>
+          <t>43119690952.3018</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>37926.433</t>
+          <t>40312688840.1415</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>51740.992</t>
+          <t>54034286753.8841</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>49698.46</t>
+          <t>51979848781.3553</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>43970.979</t>
+          <t>45378033651.4232</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>44779.044</t>
+          <t>45881851984.038</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>42402.997</t>
+          <t>44457826870.8298</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>48331.34</t>
+          <t>50328738132.6054</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>50609.385</t>
+          <t>51931406501.5054</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>48049.779</t>
+          <t>48786679180.0326</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>46934.85</t>
+          <t>47860333538.1908</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>41577.541</t>
+          <t>42793663349.1032</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>56220.049</t>
+          <t>58627474681.7847</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>57624.149</t>
+          <t>61146383435.1978</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>66441.953</t>
+          <t>70155351160.7798</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>64967.029</t>
+          <t>68496552753.5427</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>66081.347</t>
+          <t>69281324890.3309</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>51433.012</t>
+          <t>53708202364.7654</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>40919.807</t>
+          <t>42441817307.1822</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>49470.657</t>
+          <t>51573061124.7527</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>56413.137</t>
+          <t>58473519761.2512</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>56961.681</t>
+          <t>59595923551.921</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>62608.236</t>
+          <t>65626056002.1175</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>52066.878</t>
+          <t>54018076651.7782</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2284.795</t>
+          <t>2562202478.72256</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>960.696</t>
+          <t>1084308039.76699</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1643.639</t>
+          <t>1880733417.92211</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1138.222</t>
+          <t>1264627728.29253</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1070.468</t>
+          <t>1185619553.53196</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1199.492</t>
+          <t>1319949111.59143</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1140.997</t>
+          <t>1272940253.06321</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1214.622</t>
+          <t>1386386969.31732</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1317.055</t>
+          <t>1492126922.51731</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1207.863</t>
+          <t>1404066287.00131</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1231.139</t>
+          <t>1448699982.94729</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1273.087</t>
+          <t>1519055510.73564</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1546.228</t>
+          <t>1816488671.5362</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1342.82</t>
+          <t>1586819730.96065</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1396.925</t>
+          <t>1639567228.54485</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1663.622</t>
+          <t>1970880763.44668</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1652.535</t>
+          <t>1981364040.26562</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1652.264</t>
+          <t>2020843358.26342</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1572.779</t>
+          <t>1912386165.98444</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1789.073</t>
+          <t>2142529801.24004</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>1446.603</t>
+          <t>1749077428.93577</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>1462.745</t>
+          <t>1771714391.89138</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>1623.231</t>
+          <t>1979003810.40649</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1702.026</t>
+          <t>2110174303.6292</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>1820.07</t>
+          <t>2244815984.04624</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2154.845</t>
+          <t>2678451104.13125</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1844.55</t>
+          <t>2279560685.52647</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>940.256</t>
+          <t>1120119670.75844</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1011.085</t>
+          <t>1214360051.96188</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>851.636</t>
+          <t>986376547.672545</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>951.968</t>
+          <t>1115549565.23186</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>983.011</t>
+          <t>1166273030.52094</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1038.45</t>
+          <t>1248421760.19941</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1104.238</t>
+          <t>1323434411.12695</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>962.968</t>
+          <t>1132683171.34755</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1031.416</t>
+          <t>1221238476.38239</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1109.189</t>
+          <t>1331915342.09457</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1105.478</t>
+          <t>1332312815.69784</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1153.072</t>
+          <t>1396622425.87953</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1057.227</t>
+          <t>1219086830.54244</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1099.026</t>
+          <t>1254340277.08518</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1155.466</t>
+          <t>1365306701.8318</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1204.559</t>
+          <t>1440058712.1211</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1101.053</t>
+          <t>1326916938.26805</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1207.745</t>
+          <t>1491184780.57201</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1102.849</t>
+          <t>1330194551.92767</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>953.421</t>
+          <t>1162581654.72328</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>1127.55</t>
+          <t>1357797439.88213</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1000.027</t>
+          <t>1201364634.31255</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>1057.813</t>
+          <t>1298806718.52191</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1222.127</t>
+          <t>1491119185.34379</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1155.553</t>
+          <t>1398898190.05756</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>1544.762</t>
+          <t>1887150254.80912</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1271.795</t>
+          <t>1538863832.23386</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>13253.056</t>
+          <t>17433274046.59</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4466.521</t>
+          <t>5460776613.843</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4166.343</t>
+          <t>5087874791.02045</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4279.383</t>
+          <t>5259858345.19279</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4343.732</t>
+          <t>5423362499.59459</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4879.781</t>
+          <t>6118364992.25006</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5412.45</t>
+          <t>6718680564.27086</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5458.496</t>
+          <t>6813260621.81017</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5011.027</t>
+          <t>6175384589.61224</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4818.357</t>
+          <t>6009601183.68364</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4973.78</t>
+          <t>6164857613.61468</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4762.24</t>
+          <t>6021793784.18957</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4423.52</t>
+          <t>5486679665.84728</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>5034.659</t>
+          <t>6310177263.26842</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4534.888</t>
+          <t>5580341385.96677</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4111.25</t>
+          <t>5075888636.43232</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4647.072</t>
+          <t>5821587796.76332</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4887.42</t>
+          <t>6173640387.42372</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4701.682</t>
+          <t>5946555062.06949</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4784.084</t>
+          <t>6044004824.0909</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>4862.489</t>
+          <t>6143472241.51084</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>4625.365</t>
+          <t>5946047415.58871</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>4263.611</t>
+          <t>5471072504.41168</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5223.022</t>
+          <t>6702629236.41513</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>5176.543</t>
+          <t>6564916041.60221</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>5095.45</t>
+          <t>6526062974.14149</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>5368.26</t>
+          <t>6890484171.42579</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7444.215</t>
+          <t>8424806936.18812</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8220.079</t>
+          <t>9241445727.37476</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8908.096</t>
+          <t>9828438856.8281</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>9153.847</t>
+          <t>10104487823.1042</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9561.525</t>
+          <t>10549403328.2872</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10877.692</t>
+          <t>12261448914.9032</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10054.321</t>
+          <t>11446106052.91</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11703.323</t>
+          <t>13394523702.367</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11910.188</t>
+          <t>13675806254.0135</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9660.132</t>
+          <t>11268633477.1831</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10896.957</t>
+          <t>12591720671.5406</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>12416.54</t>
+          <t>14151949727.8177</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>13326.109</t>
+          <t>15689333514.1244</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>9793.383</t>
+          <t>11599279107.5023</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>11382.075</t>
+          <t>12840195691.1047</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>14831.879</t>
+          <t>16572315745.9025</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>9715.358</t>
+          <t>10912280495.7569</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>11016.027</t>
+          <t>12856138978.8006</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>14675.032</t>
+          <t>16624509681.7145</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>9041.935</t>
+          <t>10195307207.4492</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>12863.442</t>
+          <t>14608068593.3919</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>15074.806</t>
+          <t>17049575724.9869</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>14585.618</t>
+          <t>16572567556.4562</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13345.26</t>
+          <t>15287272877.4049</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>10790.315</t>
+          <t>11996253913.4249</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>7918.098</t>
+          <t>8614963277.84141</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>11289.807</t>
+          <t>12297210852.0169</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18225.031</t>
+          <t>21453789978.5261</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14012.49</t>
+          <t>15393450395.8408</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16453.4</t>
+          <t>17986120669.8233</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>18188.986</t>
+          <t>19765814139.9946</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15535.946</t>
+          <t>17039243612.5103</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21623.183</t>
+          <t>23381234129.5133</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18660.341</t>
+          <t>20456684521.8505</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>17911.12</t>
+          <t>19790201364.5294</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15156.076</t>
+          <t>16651327038.348</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>17276.157</t>
+          <t>19379739205.8782</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>15918.144</t>
+          <t>17715538938.5835</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>14009.099</t>
+          <t>15595124328.8852</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>11033.193</t>
+          <t>12129516700.5841</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>11342.909</t>
+          <t>12693677450.3385</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>8974.859</t>
+          <t>10035733760.6096</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12831.147</t>
+          <t>14265412728.8747</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12362.095</t>
+          <t>13823132187.2783</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>14736.199</t>
+          <t>16279976939.9486</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>13623.746</t>
+          <t>15233372256.0585</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>12535.612</t>
+          <t>14367120001.335</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>10974.648</t>
+          <t>12684775706.0818</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>13607.538</t>
+          <t>16101859238.2639</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>11505.127</t>
+          <t>13380548058.5507</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10614.195</t>
+          <t>12339190799.103</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>11497.899</t>
+          <t>13340868367.0095</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11540.619</t>
+          <t>13204101843.8288</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>10541.177</t>
+          <t>12368112649.8485</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>450374.042</t>
+          <t>452245322190.493</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>112009.403</t>
+          <t>120073934326.371</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>115693.915</t>
+          <t>123373252588.533</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>113579.325</t>
+          <t>123554874356.355</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>135951.879</t>
+          <t>148315189039.722</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>148760.21</t>
+          <t>161684152886.591</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>161186.839</t>
+          <t>176605221659.619</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>165792.517</t>
+          <t>181213234177.153</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>153844.374</t>
+          <t>165654854658.507</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>145245.137</t>
+          <t>159208001344.976</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>170281.903</t>
+          <t>183504633561.877</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>143166.866</t>
+          <t>156737587710.304</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>150401.192</t>
+          <t>159340768964.83</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>152030.378</t>
+          <t>163615337310.271</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>150141.508</t>
+          <t>162181712281.994</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>139426.447</t>
+          <t>150454191385.202</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>132904.453</t>
+          <t>143713825151.602</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>120597.579</t>
+          <t>133100987949.762</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>139649.253</t>
+          <t>151046195749.22</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>123805.309</t>
+          <t>133277619761.587</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>135092.058</t>
+          <t>146033207440.854</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>162402.81</t>
+          <t>174574169733.922</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>159255.583</t>
+          <t>169238817933.606</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>185339.516</t>
+          <t>199749755938.419</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>168660.658</t>
+          <t>180029649252.756</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>182873.278</t>
+          <t>197182866933.967</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>198163.582</t>
+          <t>214223612604.586</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3810300.076</t>
+          <t>3942265851125.94</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1841006.086</t>
+          <t>1923119401310.57</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2086898.006</t>
+          <t>2158366396444.42</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2494261.681</t>
+          <t>2574595771798.4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2284553.824</t>
+          <t>2383338313076.63</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2412279.666</t>
+          <t>2515592308216.03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2496897.875</t>
+          <t>2604129615408.61</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2605498.643</t>
+          <t>2704214604894.07</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2623430.614</t>
+          <t>2712560346978.97</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2452051.842</t>
+          <t>2550483201493.98</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2449584.194</t>
+          <t>2543823511569.3</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2629834.569</t>
+          <t>2720457513015.52</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2589175.461</t>
+          <t>2662341080867.92</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2598282.587</t>
+          <t>2689565053212.09</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2670070.835</t>
+          <t>2753883845354.51</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2544246.391</t>
+          <t>2631878313908.4</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2572328.406</t>
+          <t>2662872194102.29</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2550336.397</t>
+          <t>2651761855494.7</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2520050.348</t>
+          <t>2609761821122.46</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2426111.61</t>
+          <t>2521191671184.88</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2345239.213</t>
+          <t>2438626954321.08</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2818196.764</t>
+          <t>2895576728283.87</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2685358.198</t>
+          <t>2771061029902.25</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>2978292.892</t>
+          <t>3055715519350.91</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2761469.432</t>
+          <t>2844315885970.86</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>3269955.792</t>
+          <t>3346456310896.45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3399924.573</t>
+          <t>3486283475625.89</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1233.899</t>
+          <t>1512114403.21384</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1484.456</t>
+          <t>1944008201.06363</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1954.569</t>
+          <t>2322599107.94042</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2185.414</t>
+          <t>2740162196.09041</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2127.164</t>
+          <t>2648233165.95015</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2124.139</t>
+          <t>2618996057.12868</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1896.017</t>
+          <t>2266613804.7719</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1475.173</t>
+          <t>1657566292.84036</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1470.648</t>
+          <t>1640599048.5725</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1683.009</t>
+          <t>1883091955.46909</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1887.384</t>
+          <t>2118477591.32856</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1819.381</t>
+          <t>2044293786.65497</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1632.482</t>
+          <t>1863010983.75056</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1695.553</t>
+          <t>1935231283.17131</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1837.089</t>
+          <t>2133655722.21812</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1824.548</t>
+          <t>2100242371.8062</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1517.61</t>
+          <t>1722445463.64578</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1391.313</t>
+          <t>1557883691.96608</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1362.635</t>
+          <t>1508932358.9699</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1478.818</t>
+          <t>1611319130.26728</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>1298.266</t>
+          <t>1411365269.12703</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>1332.491</t>
+          <t>1426226749.86269</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1353.706</t>
+          <t>1490875004.86021</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1374.669</t>
+          <t>1572249620.81895</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1558.82</t>
+          <t>1658640173.36497</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>1699.3</t>
+          <t>1809601915.68275</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1275.622</t>
+          <t>1397471778.94419</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>7337.451</t>
+          <t>7868275310.78325</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4265.454</t>
+          <t>4705778817.50113</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4261.731</t>
+          <t>4695197339.30645</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4689.845</t>
+          <t>5166484420.87591</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4151.596</t>
+          <t>4601019516.99788</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4489.029</t>
+          <t>4940566250.37072</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4595.85</t>
+          <t>5075163208.38084</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4297.048</t>
+          <t>4884004517.9171</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4106.006</t>
+          <t>4638237230.22807</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4956.695</t>
+          <t>5608603602.38757</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>5015.663</t>
+          <t>5744446190.52636</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4506.288</t>
+          <t>5226443233.4005</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3991.393</t>
+          <t>4541359377.06309</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4796.307</t>
+          <t>5411530222.95916</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4686.881</t>
+          <t>5311794528.13955</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>5658.469</t>
+          <t>6292812844.91196</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>4919.423</t>
+          <t>5617921808.50423</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>6810.889</t>
+          <t>7581969774.48969</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>7820.11</t>
+          <t>8745334639.16088</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>5294.42</t>
+          <t>5856538518.9288</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>5329.165</t>
+          <t>5942666609.60904</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>6196.492</t>
+          <t>6826982392.3056</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>5907.91</t>
+          <t>6453545928.34041</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>5049.041</t>
+          <t>5577094655.70763</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>5300.698</t>
+          <t>5850153648.40299</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>4695.279</t>
+          <t>5151623623.62491</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>5962.826</t>
+          <t>6789786401.86492</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4344.458</t>
+          <t>4602128250.09241</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2885.217</t>
+          <t>3168466552.04352</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3305.225</t>
+          <t>3568716656.38448</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3532.051</t>
+          <t>3810978131.84161</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2753.116</t>
+          <t>3010917440.82764</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3386.336</t>
+          <t>3666931270.13895</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3359.702</t>
+          <t>3662516259.06501</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3318.038</t>
+          <t>3586323540.59336</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2994.45</t>
+          <t>3257800162.29318</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3591.526</t>
+          <t>3866250491.58381</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3433.484</t>
+          <t>3655037594.54309</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3542.882</t>
+          <t>3821731194.98388</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>4153.278</t>
+          <t>4492780272.89494</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>4618.323</t>
+          <t>5008104418.7649</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3807.979</t>
+          <t>4123635264.96701</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>3707.488</t>
+          <t>4017888480.38519</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>3829.55</t>
+          <t>4193589556.11435</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>4400.91</t>
+          <t>4796527535.3748</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>5079.003</t>
+          <t>5540797656.22997</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>4728.86</t>
+          <t>5129195889.16656</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>3559.308</t>
+          <t>3850792207.30016</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>4205.537</t>
+          <t>4511809110.9449</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>3745.011</t>
+          <t>3984697019.17042</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3809.358</t>
+          <t>4079803138.314</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>3884.172</t>
+          <t>4143408115.02678</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>4933.819</t>
+          <t>5310143725.45895</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>4563.317</t>
+          <t>4923284059.8088</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11288.611</t>
+          <t>12101553325.5278</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9360.095</t>
+          <t>9925449996.9285</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9393.077</t>
+          <t>10022429034.1676</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>8643.561</t>
+          <t>9299852399.84107</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>8902.037</t>
+          <t>9549076726.5594</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8726.453</t>
+          <t>9456941699.83759</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7292.07</t>
+          <t>7876983177.66545</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6750.388</t>
+          <t>7312611539.67779</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8496.254</t>
+          <t>9164394521.64152</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8686.294</t>
+          <t>9434066833.91857</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>8496.007</t>
+          <t>9204664809.43153</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>9253.328</t>
+          <t>10057644782.9567</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>7760.37</t>
+          <t>8264642378.47988</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>8208.451</t>
+          <t>8765563851.59653</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>7912.56</t>
+          <t>8493474928.85377</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>8122.48</t>
+          <t>8686964012.65989</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>8335.062</t>
+          <t>8919730552.15199</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>8483.714</t>
+          <t>9082668048.10892</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>8539.565</t>
+          <t>9114792613.11367</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>6703.745</t>
+          <t>7128771014.49158</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>6977.931</t>
+          <t>7432963187.76574</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>5214.771</t>
+          <t>5544287496.34442</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>7826.864</t>
+          <t>8198870692.05028</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>9560.451</t>
+          <t>9952171247.39935</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>8275.461</t>
+          <t>8590621883.06423</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>8448.502</t>
+          <t>8798566058.97584</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>7497.778</t>
+          <t>7915067341.30282</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>411747.44</t>
+          <t>422849759348.402</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>198832.178</t>
+          <t>203544330227.882</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>201262.607</t>
+          <t>204328487852.153</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>233472.92</t>
+          <t>240107243547.79</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>234261.973</t>
+          <t>244022421602.903</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>232986.647</t>
+          <t>242859934172.392</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>209834.19</t>
+          <t>219585641302.526</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>235872.1</t>
+          <t>245828453908.293</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>293216.409</t>
+          <t>307704026171.059</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>235457.113</t>
+          <t>243134843825.721</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>242277.53</t>
+          <t>249570398148.84</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>247762.831</t>
+          <t>257341433494.4</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>304831.5</t>
+          <t>320431882736.033</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>278678.402</t>
+          <t>291125074496.287</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>296335.449</t>
+          <t>310578849516.615</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>286168.092</t>
+          <t>298307146898.667</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>258962.504</t>
+          <t>268633371953.814</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>279644.576</t>
+          <t>290768484555.806</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>273512.914</t>
+          <t>280967332574.466</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>296360.518</t>
+          <t>308234683958.007</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>264950.729</t>
+          <t>277575940870.693</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>295995.758</t>
+          <t>307262534267.292</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>317429.309</t>
+          <t>329092167176.308</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>300951.011</t>
+          <t>311916348756.94</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>326419.096</t>
+          <t>335483647160.722</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>346168.437</t>
+          <t>356528195434.201</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>342814.078</t>
+          <t>355455076658.732</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>66679.442</t>
+          <t>72212154900.4568</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>49860.05</t>
+          <t>53425475627.1125</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>50835.783</t>
+          <t>54717346655.6228</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>53210.463</t>
+          <t>57165537589.6792</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>55524.793</t>
+          <t>60384894291.3264</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>54402.325</t>
+          <t>58885689241.2526</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>61949.464</t>
+          <t>67178882241.2556</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>58995.844</t>
+          <t>63974720109.7689</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>54046.652</t>
+          <t>58698285995.863</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>58429.708</t>
+          <t>63024973544.665</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>59367.62</t>
+          <t>63655166043.1534</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>59567.916</t>
+          <t>63847082698.4342</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>61150.713</t>
+          <t>65012549149.0908</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>61520.584</t>
+          <t>66363929828.3358</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>70068.886</t>
+          <t>75702408553.0241</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>72540.25</t>
+          <t>77777349151.961</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>73993.219</t>
+          <t>79192448877.2091</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>73957.965</t>
+          <t>79628528230.2022</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>78664.382</t>
+          <t>84194545729.9195</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>72672.688</t>
+          <t>77805373885.8158</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>71304.273</t>
+          <t>75845235817.2263</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>79442.952</t>
+          <t>84827858363.7189</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>73165.431</t>
+          <t>77432848595.0411</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>76476.471</t>
+          <t>81664847048.3973</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>67895.448</t>
+          <t>72278054992.6167</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>62538.264</t>
+          <t>66819373690.9869</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>59022.078</t>
+          <t>62723548717.1317</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>93887.366</t>
+          <t>112770300801.487</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>79176.363</t>
+          <t>92130272930.568</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>72774.949</t>
+          <t>83262202427.5448</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>72471.044</t>
+          <t>82935194009.2793</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>81081.161</t>
+          <t>92960729676.1899</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>72005.422</t>
+          <t>80866758639.1042</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>80094.749</t>
+          <t>89844207777.2374</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78682.551</t>
+          <t>88228997520.0766</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>71817.353</t>
+          <t>80851184033.3211</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>75894.482</t>
+          <t>85086249377.3769</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>69356.995</t>
+          <t>78048364117.8518</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>75612.216</t>
+          <t>84654065359.7788</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>89119.845</t>
+          <t>100908336152.254</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>82370.4</t>
+          <t>92923703957.3246</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>61193.776</t>
+          <t>68647731303.0805</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>69288.078</t>
+          <t>77571439097.4328</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>69657.848</t>
+          <t>78395803145.7829</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>71310.554</t>
+          <t>79363386306.6553</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>68033.47</t>
+          <t>75759993245.4818</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>67292.032</t>
+          <t>74771946451.8806</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>60201.99</t>
+          <t>66683630890.2668</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>54600.603</t>
+          <t>60688599187.4361</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>57328.518</t>
+          <t>63232475545.6956</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>55281.998</t>
+          <t>60939937211.8653</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>58655.972</t>
+          <t>64676949777.0196</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>67266.005</t>
+          <t>74193610095.6481</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>77876.593</t>
+          <t>86153901829.6391</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>410204.355</t>
+          <t>435735089679.225</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>173378.724</t>
+          <t>189762824737.754</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>177658.98</t>
+          <t>194369672958.922</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>200465.652</t>
+          <t>219785804759.488</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>195070.104</t>
+          <t>214745725956.367</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>218529.645</t>
+          <t>240791861979.444</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>226821.661</t>
+          <t>250052860275.718</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>234322.527</t>
+          <t>256161068750.927</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>241245.409</t>
+          <t>264077583751.155</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>254723.212</t>
+          <t>279435693431.082</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>265002.941</t>
+          <t>289743586190.433</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>261603.521</t>
+          <t>286013310892.06</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>213409.31</t>
+          <t>235514949492.425</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>264185.514</t>
+          <t>290453143629.047</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>269642.958</t>
+          <t>294230225362.872</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>249743.89</t>
+          <t>273630899986.54</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>293085.756</t>
+          <t>321978686439.2</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>259023.803</t>
+          <t>284421980758.112</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>268060.815</t>
+          <t>292398307464.731</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>329599.899</t>
+          <t>351176064554.353</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>335953.67</t>
+          <t>357639981506.45</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>372719.335</t>
+          <t>396988491842.533</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>311049.478</t>
+          <t>330753633744.244</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>348559.424</t>
+          <t>369815622111.776</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>348820.698</t>
+          <t>370973150250.939</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>377914.453</t>
+          <t>402214935946.898</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>400236.45</t>
+          <t>426177083620.865</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>56390.813</t>
+          <t>57855977923.7905</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18818.687</t>
+          <t>19531202166.051</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>24133.851</t>
+          <t>25152254152.6868</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25328.209</t>
+          <t>26488764553.1489</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>27731.617</t>
+          <t>29903347212.6206</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>34512.484</t>
+          <t>37261702466.9155</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>34108.188</t>
+          <t>36755518576.6107</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>41672.086</t>
+          <t>44989506085.9004</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>40195.039</t>
+          <t>42541312149.6395</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>48769.626</t>
+          <t>51974057066.3519</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>54064.498</t>
+          <t>56760150450.255</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>56889.984</t>
+          <t>60236733968.0932</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>53512.486</t>
+          <t>55917419546.1481</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>67633.663</t>
+          <t>71591794725.5758</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>66404.216</t>
+          <t>69633311754.5179</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>63117.276</t>
+          <t>66639038599.486</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>66322.48</t>
+          <t>70083513325.3025</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>72353.126</t>
+          <t>76965300733.3512</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>79376.412</t>
+          <t>83091571593.6319</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>67445.221</t>
+          <t>71042690112.6722</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>65216.701</t>
+          <t>68341256077.8667</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>72720.449</t>
+          <t>76022527162.067</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>76365.194</t>
+          <t>79512605231.625</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>81377.446</t>
+          <t>84542222450.9233</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>75184.951</t>
+          <t>78113558533.055</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>86949.997</t>
+          <t>90909492687.6348</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>86841.98</t>
+          <t>91016206784.9022</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
